--- a/hardis-report/xls/backup-updated-files-monitoring_orgfarm_42750320ff_dev_ed_develop.xlsx
+++ b/hardis-report/xls/backup-updated-files-monitoring_orgfarm_42750320ff_dev_ed_develop.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>File</t>
   </si>
@@ -50,75 +50,6 @@
   </si>
   <si>
     <t>📰</t>
-  </si>
-  <si>
-    <t>layouts/Installation__c-Installation Layout.layout-meta.xml</t>
-  </si>
-  <si>
-    <t>Layout Installation__c-Installation Layout</t>
-  </si>
-  <si>
-    <t>layouts/Panel_Batch__c-Panel Batch Layout.layout-meta.xml</t>
-  </si>
-  <si>
-    <t>Layout Panel_Batch__c-Panel Batch Layout</t>
-  </si>
-  <si>
-    <t>objects/Installation__c/fields/Gate_Code__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>CustomFieldTranslation Gate_Code__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>objects/Installation__c/fields/Install_Date__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>CustomFieldTranslation Install_Date__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>objects/Installation__c/fields/Scaffolding_Required__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>CustomFieldTranslation Scaffolding_Required__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>objects/Installation__c/fields/Status__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>CustomFieldTranslation Status__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>objects/Panel_Batch__c/fields/Supplier__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>CustomFieldTranslation Supplier__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>objects/Panel_Batch__c/fields/Warranty_Years__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>CustomFieldTranslation Warranty_Years__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>permissionsets/Helios_Delivery_Crew.permissionset-meta.xml</t>
-  </si>
-  <si>
-    <t>PermissionSet Helios_Delivery_Crew</t>
-  </si>
-  <si>
-    <t>permissionsets/Helios_Delivery_Manager.permissionset-meta.xml</t>
-  </si>
-  <si>
-    <t>PermissionSet Helios_Delivery_Manager</t>
-  </si>
-  <si>
-    <t>manifest/package-all-org-items.xml</t>
-  </si>
-  <si>
-    <t>manifest/package-backup-items.xml</t>
   </si>
 </sst>
 </file>
@@ -180,8 +111,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Table_sheet1_1" displayName="Table_sheet1_1" ref="A1:G14" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:G14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Table_sheet1_1" displayName="Table_sheet1_1" ref="A1:G2" totalsRowShown="1" headerRowCount="1">
+  <autoFilter ref="A1:G2">
     <filterColumn colId="0" hiddenButton="0"/>
     <filterColumn colId="1" hiddenButton="0"/>
     <filterColumn colId="2" hiddenButton="0"/>
@@ -525,12 +456,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="60" style="1" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="60" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
@@ -543,7 +474,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -566,7 +497,7 @@
       <c r="B2" s="2">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -579,282 +510,6 @@
         <v>11</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="2" t="s">
         <v>12</v>
       </c>
     </row>

--- a/hardis-report/xls/backup-updated-files-monitoring_orgfarm_42750320ff_dev_ed_develop.xlsx
+++ b/hardis-report/xls/backup-updated-files-monitoring_orgfarm_42750320ff_dev_ed_develop.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="80">
   <si>
     <t>File</t>
   </si>
@@ -50,6 +50,207 @@
   </si>
   <si>
     <t>📰</t>
+  </si>
+  <si>
+    <t>notificationTypeConfig/NotificationTypeConfig.config-meta.xml</t>
+  </si>
+  <si>
+    <t>NotificationTypeConfig NotificationTypeConfig</t>
+  </si>
+  <si>
+    <t>profiles/Admin.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Admin</t>
+  </si>
+  <si>
+    <t>profiles/Anypoint Integration.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Anypoint Integration</t>
+  </si>
+  <si>
+    <t>profiles/Authenticated Website.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Authenticated Website</t>
+  </si>
+  <si>
+    <t>profiles/ContractManager.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile ContractManager</t>
+  </si>
+  <si>
+    <t>profiles/Customer Community Login User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Customer Community Login User</t>
+  </si>
+  <si>
+    <t>profiles/Customer Community Plus Login User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Customer Community Plus Login User</t>
+  </si>
+  <si>
+    <t>profiles/Customer Community Plus User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Customer Community Plus User</t>
+  </si>
+  <si>
+    <t>profiles/Customer Community User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Customer Community User</t>
+  </si>
+  <si>
+    <t>profiles/Customer Portal Manager Custom.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Customer Portal Manager Custom</t>
+  </si>
+  <si>
+    <t>profiles/Customer Portal Manager Standard.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Customer Portal Manager Standard</t>
+  </si>
+  <si>
+    <t>profiles/External Apps Login User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile External Apps Login User</t>
+  </si>
+  <si>
+    <t>profiles/External Identity User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile External Identity User</t>
+  </si>
+  <si>
+    <t>profiles/Gold Partner User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Gold Partner User</t>
+  </si>
+  <si>
+    <t>profiles/Helios Crew.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Helios Crew</t>
+  </si>
+  <si>
+    <t>profiles/High Volume Customer Portal User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile High Volume Customer Portal User</t>
+  </si>
+  <si>
+    <t>profiles/HighVolumePortal.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile HighVolumePortal</t>
+  </si>
+  <si>
+    <t>profiles/Identity User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Identity User</t>
+  </si>
+  <si>
+    <t>profiles/MarketingProfile.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile MarketingProfile</t>
+  </si>
+  <si>
+    <t>profiles/Minimum Access - API Only Integrations.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Minimum Access - API Only Integrations</t>
+  </si>
+  <si>
+    <t>profiles/Minimum Access - Salesforce.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Minimum Access - Salesforce</t>
+  </si>
+  <si>
+    <t>profiles/Partner Community Login User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Partner Community Login User</t>
+  </si>
+  <si>
+    <t>profiles/Partner Community User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Partner Community User</t>
+  </si>
+  <si>
+    <t>profiles/PlatformPortal.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile PlatformPortal</t>
+  </si>
+  <si>
+    <t>profiles/Silver Partner User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Silver Partner User</t>
+  </si>
+  <si>
+    <t>profiles/SolutionManager.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile SolutionManager</t>
+  </si>
+  <si>
+    <t>profiles/Standard.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Standard</t>
+  </si>
+  <si>
+    <t>settings/CustomerIntelligence.settings-meta.xml</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Settings CustomerIntelligence</t>
+  </si>
+  <si>
+    <t>settings/IncidentMgmt.settings-meta.xml</t>
+  </si>
+  <si>
+    <t>Settings IncidentMgmt</t>
+  </si>
+  <si>
+    <t>settings/MCETransformations.settings-meta.xml</t>
+  </si>
+  <si>
+    <t>Settings MCETransformations</t>
+  </si>
+  <si>
+    <t>settings/SelfService.settings-meta.xml</t>
+  </si>
+  <si>
+    <t>Settings SelfService</t>
+  </si>
+  <si>
+    <t>sharingRules/UiPageAuthoringConv.sharingRules-meta.xml</t>
+  </si>
+  <si>
+    <t>SharingTerritoryRule UiPageAuthoringConv.sharingRules-meta.xml</t>
+  </si>
+  <si>
+    <t>manifest/package-all-org-items.xml</t>
+  </si>
+  <si>
+    <t>manifest/package-backup-items.xml</t>
   </si>
 </sst>
 </file>
@@ -111,8 +312,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Table_sheet1_1" displayName="Table_sheet1_1" ref="A1:G2" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:G2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Table_sheet1_1" displayName="Table_sheet1_1" ref="A1:G36" totalsRowShown="1" headerRowCount="1">
+  <autoFilter ref="A1:G36">
     <filterColumn colId="0" hiddenButton="0"/>
     <filterColumn colId="1" hiddenButton="0"/>
     <filterColumn colId="2" hiddenButton="0"/>
@@ -456,12 +657,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="60" style="1" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="3" max="3" width="60" style="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
@@ -474,7 +675,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -497,7 +698,7 @@
       <c r="B2" s="2">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -510,6 +711,788 @@
         <v>11</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>12</v>
       </c>
     </row>

--- a/hardis-report/xls/backup-updated-files-monitoring_orgfarm_42750320ff_dev_ed_develop.xlsx
+++ b/hardis-report/xls/backup-updated-files-monitoring_orgfarm_42750320ff_dev_ed_develop.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="51">
   <si>
     <t>File</t>
   </si>
@@ -50,6 +50,120 @@
   </si>
   <si>
     <t>📰</t>
+  </si>
+  <si>
+    <t>profiles/Analytics Cloud Integration User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Analytics Cloud Integration User</t>
+  </si>
+  <si>
+    <t>profiles/Analytics Cloud Security User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Analytics Cloud Security User</t>
+  </si>
+  <si>
+    <t>profiles/B2B Reordering Portal Buyer Profile.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile B2B Reordering Portal Buyer Profile</t>
+  </si>
+  <si>
+    <t>profiles/Chatter External User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Chatter External User</t>
+  </si>
+  <si>
+    <t>profiles/Chatter Free User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Chatter Free User</t>
+  </si>
+  <si>
+    <t>profiles/Chatter Moderator User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Chatter Moderator User</t>
+  </si>
+  <si>
+    <t>profiles/Cross Org Data Proxy User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Cross Org Data Proxy User</t>
+  </si>
+  <si>
+    <t>profiles/Custom%3A Marketing Profile.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Custom%3A Marketing Profile</t>
+  </si>
+  <si>
+    <t>profiles/Custom%3A Sales Profile.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Custom%3A Sales Profile</t>
+  </si>
+  <si>
+    <t>profiles/Custom%3A Support Profile.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Custom%3A Support Profile</t>
+  </si>
+  <si>
+    <t>profiles/Einstein Agent User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Einstein Agent User</t>
+  </si>
+  <si>
+    <t>profiles/External Einstein Agent User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile External Einstein Agent User</t>
+  </si>
+  <si>
+    <t>profiles/Force%2Ecom - App Subscription User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Force%2Ecom - App Subscription User</t>
+  </si>
+  <si>
+    <t>profiles/Force%2Ecom - Free User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Force%2Ecom - Free User</t>
+  </si>
+  <si>
+    <t>profiles/Partner App Subscription User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Partner App Subscription User</t>
+  </si>
+  <si>
+    <t>profiles/Read Only.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Read Only</t>
+  </si>
+  <si>
+    <t>profiles/Salesforce API Only System Integrations.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Salesforce API Only System Integrations</t>
+  </si>
+  <si>
+    <t>profiles/StandardAul.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile StandardAul</t>
+  </si>
+  <si>
+    <t>profiles/Work%2Ecom Only User.profile-meta.xml</t>
+  </si>
+  <si>
+    <t>Profile Work%2Ecom Only User</t>
   </si>
 </sst>
 </file>
@@ -111,8 +225,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Table_sheet1_1" displayName="Table_sheet1_1" ref="A1:G2" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:G2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Table_sheet1_1" displayName="Table_sheet1_1" ref="A1:G21" totalsRowShown="1" headerRowCount="1">
+  <autoFilter ref="A1:G21">
     <filterColumn colId="0" hiddenButton="0"/>
     <filterColumn colId="1" hiddenButton="0"/>
     <filterColumn colId="2" hiddenButton="0"/>
@@ -456,12 +570,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="60" style="1" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
@@ -510,6 +624,443 @@
         <v>11</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>12</v>
       </c>
     </row>
